--- a/src/test/java/ParaBank/TestRunner/ParaBankData/ParaBank_data.xlsx
+++ b/src/test/java/ParaBank/TestRunner/ParaBankData/ParaBank_data.xlsx
@@ -47,34 +47,34 @@
     <t>confirmPassword</t>
   </si>
   <si>
-    <t>Shondra</t>
+    <t>Maynard</t>
   </si>
   <si>
-    <t>O'Reilly</t>
+    <t>Cummings</t>
   </si>
   <si>
-    <t>67610 Spinka Locks</t>
+    <t>61035 Daron Mount</t>
   </si>
   <si>
-    <t>Reichelmouth</t>
+    <t>Lake Lillia</t>
   </si>
   <si>
-    <t>Georgia</t>
+    <t>Massachusetts</t>
   </si>
   <si>
-    <t>37088-8954</t>
+    <t>65380-5828</t>
   </si>
   <si>
-    <t>341.937.3592</t>
+    <t>546-740-9810</t>
   </si>
   <si>
-    <t>B000A6LR6K</t>
+    <t>B000A3PI3G</t>
   </si>
   <si>
-    <t>moshe.jast</t>
+    <t>boyce.mills</t>
   </si>
   <si>
-    <t>ib4mz1gcw</t>
+    <t>4d3ftm8a099c6os</t>
   </si>
 </sst>
 </file>
